--- a/config/excel/hero.xlsx
+++ b/config/excel/hero.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
   <si>
     <t xml:space="preserve"> 字段</t>
   </si>
@@ -50,9 +50,6 @@
     <t>图标</t>
   </si>
   <si>
-    <t>抽奖概率</t>
-  </si>
-  <si>
     <t>对应的碎片数量</t>
   </si>
   <si>
@@ -101,13 +98,10 @@
     <t>icon</t>
   </si>
   <si>
-    <t>prob</t>
-  </si>
-  <si>
-    <t>shard</t>
-  </si>
-  <si>
-    <t>item</t>
+    <t>shardAmount</t>
+  </si>
+  <si>
+    <t>ShardItem</t>
   </si>
   <si>
     <t>skills</t>
@@ -1440,7 +1434,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="7.375" customWidth="1"/>
@@ -1449,13 +1443,12 @@
     <col min="5" max="5" width="24.125" customWidth="1"/>
     <col min="6" max="6" width="70.25" customWidth="1"/>
     <col min="7" max="7" width="18.5416666666667" customWidth="1"/>
-    <col min="8" max="8" width="8.875" customWidth="1"/>
-    <col min="9" max="9" width="16.875" customWidth="1"/>
-    <col min="10" max="10" width="7.375" customWidth="1"/>
-    <col min="11" max="11" width="49.25" customWidth="1"/>
+    <col min="8" max="8" width="16.875" customWidth="1"/>
+    <col min="9" max="9" width="22.625" customWidth="1"/>
+    <col min="10" max="10" width="49.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1498,107 +1491,98 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="B2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
       <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>15</v>
+      <c r="H2" t="s">
+        <v>14</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J2" t="s">
         <v>15</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>15</v>
+      <c r="B3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:14">
       <c r="B4">
         <v>1001</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1607,7 +1591,7 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G4">
         <v>1001</v>
@@ -1616,21 +1600,18 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
         <v>1001</v>
       </c>
-      <c r="K4" t="s">
-        <v>34</v>
+      <c r="J4" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:14">
       <c r="B5">
         <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1639,7 +1620,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G5">
         <v>1002</v>
@@ -1648,21 +1629,18 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
         <v>1002</v>
       </c>
-      <c r="K5" t="s">
-        <v>37</v>
+      <c r="J5" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:14">
       <c r="B6">
         <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1671,7 +1649,7 @@
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G6">
         <v>1003</v>
@@ -1680,21 +1658,18 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
         <v>1003</v>
       </c>
-      <c r="K6" t="s">
-        <v>40</v>
+      <c r="J6" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="7" ht="17.25" spans="1:15">
+    <row r="7" ht="17.25" spans="1:14">
       <c r="B7">
         <v>1004</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1703,7 +1678,7 @@
         <v>4</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G7">
         <v>1004</v>
@@ -1712,21 +1687,18 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
         <v>1004</v>
       </c>
-      <c r="K7" t="s">
-        <v>43</v>
+      <c r="J7" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:14">
       <c r="B8">
         <v>1005</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1735,42 +1707,39 @@
         <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G8">
         <v>1005</v>
       </c>
       <c r="H8">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="I8">
-        <v>14</v>
-      </c>
-      <c r="J8">
         <v>1005</v>
       </c>
-      <c r="K8" t="s">
-        <v>46</v>
+      <c r="J8" t="s">
+        <v>44</v>
+      </c>
+      <c r="K8">
+        <v>1000</v>
       </c>
       <c r="L8">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="M8">
         <v>250</v>
       </c>
       <c r="N8">
-        <v>250</v>
-      </c>
-      <c r="O8">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:14">
       <c r="B9">
         <v>1006</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D9">
         <v>3</v>
@@ -1779,42 +1748,39 @@
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G9">
         <v>1006</v>
       </c>
       <c r="H9">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="I9">
-        <v>15</v>
-      </c>
-      <c r="J9">
         <v>1006</v>
       </c>
-      <c r="K9" t="s">
-        <v>49</v>
+      <c r="J9" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9">
+        <v>1000</v>
       </c>
       <c r="L9">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="M9">
         <v>180</v>
       </c>
       <c r="N9">
-        <v>180</v>
-      </c>
-      <c r="O9">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:14">
       <c r="B10">
         <v>1007</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1823,42 +1789,39 @@
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G10">
         <v>1007</v>
       </c>
       <c r="H10">
+        <v>12</v>
+      </c>
+      <c r="I10">
+        <v>1007</v>
+      </c>
+      <c r="J10" t="s">
+        <v>50</v>
+      </c>
+      <c r="K10">
         <v>500</v>
       </c>
-      <c r="I10">
-        <v>12</v>
-      </c>
-      <c r="J10">
-        <v>1007</v>
-      </c>
-      <c r="K10" t="s">
-        <v>52</v>
-      </c>
       <c r="L10">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="M10">
         <v>80</v>
       </c>
       <c r="N10">
-        <v>80</v>
-      </c>
-      <c r="O10">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:14">
       <c r="B11">
         <v>1008</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -1867,42 +1830,39 @@
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G11">
         <v>1008</v>
       </c>
       <c r="H11">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="I11">
-        <v>17</v>
-      </c>
-      <c r="J11">
         <v>1008</v>
       </c>
-      <c r="K11" t="s">
-        <v>55</v>
+      <c r="J11" t="s">
+        <v>53</v>
+      </c>
+      <c r="K11">
+        <v>800</v>
       </c>
       <c r="L11">
-        <v>800</v>
+        <v>180</v>
       </c>
       <c r="M11">
         <v>180</v>
       </c>
       <c r="N11">
-        <v>180</v>
-      </c>
-      <c r="O11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:14">
       <c r="B12">
         <v>1009</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D12">
         <v>4</v>
@@ -1911,42 +1871,39 @@
         <v>4</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G12">
         <v>1009</v>
       </c>
       <c r="H12">
-        <v>500</v>
+        <v>18</v>
       </c>
       <c r="I12">
-        <v>18</v>
-      </c>
-      <c r="J12">
         <v>1009</v>
       </c>
-      <c r="K12" t="s">
-        <v>58</v>
+      <c r="J12" t="s">
+        <v>56</v>
+      </c>
+      <c r="K12">
+        <v>400</v>
       </c>
       <c r="L12">
-        <v>400</v>
+        <v>70</v>
       </c>
       <c r="M12">
         <v>70</v>
       </c>
       <c r="N12">
-        <v>70</v>
-      </c>
-      <c r="O12">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:14">
       <c r="B13">
         <v>1010</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -1955,42 +1912,39 @@
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G13">
         <v>1010</v>
       </c>
       <c r="H13">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="I13">
-        <v>19</v>
-      </c>
-      <c r="J13">
         <v>1010</v>
       </c>
-      <c r="K13" t="s">
-        <v>61</v>
+      <c r="J13" t="s">
+        <v>59</v>
+      </c>
+      <c r="K13">
+        <v>800</v>
       </c>
       <c r="L13">
-        <v>800</v>
+        <v>170</v>
       </c>
       <c r="M13">
         <v>170</v>
       </c>
       <c r="N13">
-        <v>170</v>
-      </c>
-      <c r="O13">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:14">
       <c r="B14">
         <v>1011</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1999,42 +1953,39 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G14">
         <v>1011</v>
       </c>
       <c r="H14">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="I14">
-        <v>11</v>
-      </c>
-      <c r="J14">
         <v>1011</v>
       </c>
-      <c r="K14" t="s">
-        <v>61</v>
+      <c r="J14" t="s">
+        <v>59</v>
+      </c>
+      <c r="K14">
+        <v>1000</v>
       </c>
       <c r="L14">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="M14">
         <v>200</v>
       </c>
       <c r="N14">
-        <v>200</v>
-      </c>
-      <c r="O14">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:14">
       <c r="B15">
         <v>1012</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -2043,45 +1994,42 @@
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G15">
         <v>1012</v>
       </c>
       <c r="H15">
+        <v>20</v>
+      </c>
+      <c r="I15">
+        <v>1012</v>
+      </c>
+      <c r="J15" t="s">
+        <v>64</v>
+      </c>
+      <c r="K15">
         <v>500</v>
       </c>
-      <c r="I15">
-        <v>20</v>
-      </c>
-      <c r="J15">
-        <v>1012</v>
-      </c>
-      <c r="K15" t="s">
-        <v>66</v>
-      </c>
       <c r="L15">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M15">
         <v>100</v>
       </c>
       <c r="N15">
-        <v>100</v>
-      </c>
-      <c r="O15">
         <v>10</v>
       </c>
     </row>
-    <row r="16" customFormat="1" spans="1:15">
+    <row r="16" customFormat="1" spans="1:14">
       <c r="A16" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B16">
         <v>1013</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -2090,33 +2038,30 @@
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G16">
         <v>1013</v>
       </c>
       <c r="H16">
-        <v>500</v>
+        <v>13</v>
       </c>
       <c r="I16">
-        <v>13</v>
-      </c>
-      <c r="J16">
         <v>1013</v>
       </c>
-      <c r="K16" t="s">
-        <v>70</v>
+      <c r="J16" t="s">
+        <v>68</v>
+      </c>
+      <c r="K16">
+        <v>800</v>
       </c>
       <c r="L16">
-        <v>800</v>
+        <v>180</v>
       </c>
       <c r="M16">
         <v>180</v>
       </c>
       <c r="N16">
-        <v>180</v>
-      </c>
-      <c r="O16">
         <v>10</v>
       </c>
     </row>
